--- a/artfynd/A 31030-2025 artfynd.xlsx
+++ b/artfynd/A 31030-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126379755</v>
+        <v>126379758</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>80109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755212</v>
+        <v>755181</v>
       </c>
       <c r="R2" t="n">
-        <v>7350820</v>
+        <v>7350738</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379758</v>
+        <v>126379754</v>
       </c>
       <c r="B3" t="n">
-        <v>80109</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755181</v>
+        <v>755384</v>
       </c>
       <c r="R3" t="n">
-        <v>7350738</v>
+        <v>7350807</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126379754</v>
+        <v>126379755</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755384</v>
+        <v>755212</v>
       </c>
       <c r="R4" t="n">
-        <v>7350807</v>
+        <v>7350820</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 31030-2025 artfynd.xlsx
+++ b/artfynd/A 31030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126379758</v>
       </c>
       <c r="B2" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379754</v>
+        <v>126379755</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755384</v>
+        <v>755212</v>
       </c>
       <c r="R3" t="n">
-        <v>7350807</v>
+        <v>7350820</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126379755</v>
+        <v>126379754</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755212</v>
+        <v>755384</v>
       </c>
       <c r="R4" t="n">
-        <v>7350820</v>
+        <v>7350807</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -996,7 +996,7 @@
         <v>126379757</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>126379760</v>
       </c>
       <c r="B6" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>126379756</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126379761</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>126379752</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>126379759</v>
       </c>
       <c r="B10" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31030-2025 artfynd.xlsx
+++ b/artfynd/A 31030-2025 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379755</v>
+        <v>126379754</v>
       </c>
       <c r="B3" t="n">
-        <v>98278</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755212</v>
+        <v>755384</v>
       </c>
       <c r="R3" t="n">
-        <v>7350820</v>
+        <v>7350807</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126379754</v>
+        <v>126379755</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755384</v>
+        <v>755212</v>
       </c>
       <c r="R4" t="n">
-        <v>7350807</v>
+        <v>7350820</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 31030-2025 artfynd.xlsx
+++ b/artfynd/A 31030-2025 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379754</v>
+        <v>126379755</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755384</v>
+        <v>755212</v>
       </c>
       <c r="R3" t="n">
-        <v>7350807</v>
+        <v>7350820</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126379755</v>
+        <v>126379754</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755212</v>
+        <v>755384</v>
       </c>
       <c r="R4" t="n">
-        <v>7350820</v>
+        <v>7350807</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 31030-2025 artfynd.xlsx
+++ b/artfynd/A 31030-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126379758</v>
+        <v>126379759</v>
       </c>
       <c r="B2" t="n">
-        <v>80112</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755181</v>
+        <v>755134</v>
       </c>
       <c r="R2" t="n">
-        <v>7350738</v>
+        <v>7350780</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379755</v>
+        <v>126379758</v>
       </c>
       <c r="B3" t="n">
-        <v>98278</v>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755212</v>
+        <v>755181</v>
       </c>
       <c r="R3" t="n">
-        <v>7350820</v>
+        <v>7350738</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126379754</v>
+        <v>126379755</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755384</v>
+        <v>755212</v>
       </c>
       <c r="R4" t="n">
-        <v>7350807</v>
+        <v>7350820</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126379757</v>
+        <v>126379761</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755429</v>
+        <v>755132</v>
       </c>
       <c r="R5" t="n">
-        <v>7350791</v>
+        <v>7350816</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126379760</v>
+        <v>126379752</v>
       </c>
       <c r="B6" t="n">
-        <v>98382</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755132</v>
+        <v>755342</v>
       </c>
       <c r="R6" t="n">
-        <v>7350824</v>
+        <v>7350787</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126379756</v>
+        <v>126379754</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755398</v>
+        <v>755384</v>
       </c>
       <c r="R7" t="n">
-        <v>7350838</v>
+        <v>7350807</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126379761</v>
+        <v>126379756</v>
       </c>
       <c r="B8" t="n">
-        <v>98278</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755132</v>
+        <v>755398</v>
       </c>
       <c r="R8" t="n">
-        <v>7350816</v>
+        <v>7350838</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126379752</v>
+        <v>126379757</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755342</v>
+        <v>755429</v>
       </c>
       <c r="R9" t="n">
-        <v>7350787</v>
+        <v>7350791</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1523,32 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126379759</v>
+        <v>126379760</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>99140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>755134</v>
+        <v>755132</v>
       </c>
       <c r="R10" t="n">
-        <v>7350780</v>
+        <v>7350824</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 31030-2025 artfynd.xlsx
+++ b/artfynd/A 31030-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379759</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379758</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379755</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379761</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379752</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379754</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379756</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379757</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,8 +1671,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379760</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>